--- a/partner_results/chebi/ClassMissingGermanLabel_chebi.xlsx
+++ b/partner_results/chebi/ClassMissingGermanLabel_chebi.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rubber particle [chebi]</t>
+          <t>hydrocarbylene group [chebi]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>polymer [chebi]</t>
+          <t>organodiyl group [chebi]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A polymer consisting of cis-linked prenyl units.</t>
+          <t>A bivalent group formed by removing two hydrogen atoms from a hydrocarbon, the free valencies of which are not engaged in a double bond.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hydrocarbylene group [chebi]</t>
+          <t>organic divalent group [chebi]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>organic group [chebi]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lars Vogt</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A bivalent group formed by removing two hydrogen atoms from a hydrocarbon, the free valencies of which are not engaged in a double bond.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -489,7 +493,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>organosulfur heterocyclic compound</t>
+          <t>azole</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -503,37 +507,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>organodiyl group [chebi]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>organic divalent group [chebi]</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>organic group [chebi]</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Lars Vogt</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Any organic substituent group, regardless of functional type, having two free valences at carbon atom(s).</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
+          <t>rubber particle [chebi]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>organic divalent group [chebi]</t>
+          <t>polymer [chebi]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Any organic substituent group, regardless of functional type, having two free valences at carbon atom(s).</t>
+          <t>A polymer consisting of cis-linked prenyl units.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
